--- a/ig/DM-DECEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-DECEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -6232,7 +6232,7 @@
     <t>0974</t>
   </si>
   <si>
-    <t>Réadaptation de la Mucoviscidose</t>
+    <t>Rééducation de la Mucoviscidose</t>
   </si>
   <si>
     <t>0975</t>

--- a/ig/DM-DECEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-DECEMBRE-2025/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -9625,7 +9625,7 @@
     <t>1454</t>
   </si>
   <si>
-    <t>Evaluation et suivi standardisé des commotions cérébrales dans un cadre sportif</t>
+    <t>Evaluation et suivi standardisé clinique et paraclinique des commotions cérébrales (Traumatisme Crânien Léger - TCL) dans un cadre sportif</t>
   </si>
   <si>
     <t>1455</t>
@@ -9703,7 +9703,7 @@
     <t>1467</t>
   </si>
   <si>
-    <t>Evaluation de la vue du sportif </t>
+    <t>Evaluation de la vue du sportif</t>
   </si>
   <si>
     <t>1468</t>
